--- a/Result/profitability/3652.xlsx
+++ b/Result/profitability/3652.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>0.54</v>
+        <v>0.5975</v>
       </c>
       <c r="N2" t="n">
-        <v>35.4375</v>
+        <v>35.35875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.63875</v>
+        <v>0.67875</v>
       </c>
       <c r="N3" t="n">
-        <v>35.6675</v>
+        <v>35.76625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61375</v>
+        <v>0.66125</v>
       </c>
       <c r="N4" t="n">
-        <v>36.18</v>
+        <v>36.2075</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.2</v>
       </c>
       <c r="M5" t="n">
-        <v>0.54625</v>
+        <v>0.6275000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>36.6875</v>
+        <v>36.4875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.50625</v>
+        <v>0.53</v>
       </c>
       <c r="N6" t="n">
-        <v>37.375</v>
+        <v>37.32125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.48375</v>
+        <v>0.5237499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>37.26</v>
+        <v>37.53875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5125</v>
+        <v>0.5525</v>
       </c>
       <c r="N8" t="n">
-        <v>38.34</v>
+        <v>38.26374999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.23</v>
       </c>
       <c r="M10" t="n">
-        <v>0.31</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>38.13</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3652</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>761</v>
+      </c>
+      <c r="D75" t="n">
+        <v>500</v>
+      </c>
+      <c r="E75" t="n">
+        <v>261</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>63</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" t="n">
+        <v>68</v>
+      </c>
+      <c r="K75" t="n">
+        <v>54</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.31375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6099999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01746849942726225</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>9.285714285714285</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.599999999999994</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.04455583402951813</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
